--- a/artfynd/A 18983-2025 artfynd.xlsx
+++ b/artfynd/A 18983-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129518715</v>
       </c>
       <c r="B2" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18983-2025 artfynd.xlsx
+++ b/artfynd/A 18983-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129518715</v>
       </c>
       <c r="B2" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18983-2025 artfynd.xlsx
+++ b/artfynd/A 18983-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129518715</v>
       </c>
       <c r="B2" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18983-2025 artfynd.xlsx
+++ b/artfynd/A 18983-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129518715</v>
       </c>
       <c r="B2" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
